--- a/branches/updated-examples/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/branches/updated-examples/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:uuid:3f82e709-17e1-4ced-9c2c-f5a9cc7e6288</t>
+    <t>urn:uuid:301d535a-2818-4148-8276-1545e5dd8d77</t>
   </si>
   <si>
     <t>Version</t>

--- a/branches/updated-examples/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/branches/updated-examples/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:uuid:301d535a-2818-4148-8276-1545e5dd8d77</t>
+    <t>urn:uuid:ad70f35e-c932-4f75-affa-a418490daecf</t>
   </si>
   <si>
     <t>Version</t>

--- a/branches/updated-examples/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/branches/updated-examples/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:uuid:ad70f35e-c932-4f75-affa-a418490daecf</t>
+    <t>urn:uuid:06a690e4-cdd0-426d-a6af-fc0ddfa1424f</t>
   </si>
   <si>
     <t>Version</t>

--- a/branches/updated-examples/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/branches/updated-examples/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:uuid:06a690e4-cdd0-426d-a6af-fc0ddfa1424f</t>
+    <t>urn:uuid:967a5991-0eaa-4e4f-b8b4-38caca83d396</t>
   </si>
   <si>
     <t>Version</t>

--- a/branches/updated-examples/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/branches/updated-examples/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:uuid:967a5991-0eaa-4e4f-b8b4-38caca83d396</t>
+    <t>urn:uuid:867afd54-c338-4e54-82b2-3a8a789419fd</t>
   </si>
   <si>
     <t>Version</t>

--- a/branches/updated-examples/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/branches/updated-examples/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:uuid:867afd54-c338-4e54-82b2-3a8a789419fd</t>
+    <t>urn:uuid:af3502db-f3ef-4eb8-b6dc-1257b145f2cf</t>
   </si>
   <si>
     <t>Version</t>

--- a/branches/updated-examples/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/branches/updated-examples/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:uuid:af3502db-f3ef-4eb8-b6dc-1257b145f2cf</t>
+    <t>urn:uuid:c6c13927-2fa0-451b-a403-4a31c7a652ea</t>
   </si>
   <si>
     <t>Version</t>

--- a/branches/updated-examples/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/branches/updated-examples/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:uuid:c6c13927-2fa0-451b-a403-4a31c7a652ea</t>
+    <t>urn:uuid:ede819df-e975-445e-a2d2-9aa6068a5e88</t>
   </si>
   <si>
     <t>Version</t>

--- a/branches/updated-examples/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/branches/updated-examples/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:uuid:ede819df-e975-445e-a2d2-9aa6068a5e88</t>
+    <t>urn:uuid:956bfe92-0223-4e91-953f-6332d6c67736</t>
   </si>
   <si>
     <t>Version</t>

--- a/branches/updated-examples/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/branches/updated-examples/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:uuid:956bfe92-0223-4e91-953f-6332d6c67736</t>
+    <t>urn:uuid:2e99e97e-dc25-4736-b324-b2ed19384b89</t>
   </si>
   <si>
     <t>Version</t>

--- a/branches/updated-examples/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
+++ b/branches/updated-examples/ValueSet-q-collect-information-a_q-collect-information-a.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:uuid:2e99e97e-dc25-4736-b324-b2ed19384b89</t>
+    <t>urn:uuid:293ff821-ef38-43d0-9c74-58fef8124621</t>
   </si>
   <si>
     <t>Version</t>
